--- a/video_history.xlsx
+++ b/video_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,6 +636,534 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:08:16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>video_ok\violation_614_1786352887.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:08:39</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>video_ng\violation_615_1786352912.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:18:21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>video_ng\violation_618_1786353493.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:19:08</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>video_ng\violation_622_1786353539.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:19:21</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>video_ng\violation_622_1786353554.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:20:23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>video_ok\violation_626_1786353616.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:20:32</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>video_ok\violation_629_1786353624.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:20:55</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>video_ok\violation_632_1786353646.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:21:02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>video_ok\violation_633_1786353653.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:22:24</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>video_ng\violation_641_1786353736.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:24:16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>video_ng\violation_648_1786353849.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:24:38</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>video_ng\violation_661_1786353870.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:25:45</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>video_ng\violation_671_1786353937.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:25:52</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>video_ng\violation_675_1786353945.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:25:56</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>video_ng\violation_684_1786353949.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:26:45</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>video_ok\violation_685_1786353996.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:28:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>video_ok\violation_686_1786354072.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:28:57</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>video_ng\violation_687_1786354127.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:30:02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>video_ok\violation_692_1786354190.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:30:18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>video_ok\violation_697_1786354208.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:30:42</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>video_ng\violation_698_1786354231.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:32:24</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>video_ok\violation_710_1786354334.webm</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:35:20</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>video_ng\violation_711_1786354513.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:35:37</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Camera_1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>video_ok\violation_712_1786354530.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
